--- a/docs/06_api_test_cases.xlsx
+++ b/docs/06_api_test_cases.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -910,6 +910,80 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>TC-API-011</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>REQ-API-011</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>İsimle filtreleme</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>GET /booking?firstname=Sally&amp;lastname=Brown</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Response bir dizi olup her eleman bookingid içerir (filtre çalışır, dizi döner)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>TC-API-012</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>REQ-API-012</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Tarihle filtreleme</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>GET /booking?checkin=2014-01-01&amp;checkout=2015-01-01</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Response bir dizi olup her eleman bookingid içerir (tarih filtresi çalışır)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
